--- a/jogos_2025-09-28.xlsx
+++ b/jogos_2025-09-28.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N65" t="n">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="M69" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N69" t="n">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,16 +11544,16 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,61 +13053,61 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M117" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="N117" t="n">
-        <v>9.6</v>
+        <v>3.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,16 +16317,16 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,16 +16446,16 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z138" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>
@@ -18306,22 +18306,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,22 +19983,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,22 +21144,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z162" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA162" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23805,10 +23805,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24321,10 +24321,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,22 +24498,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,22 +24756,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,22 +24885,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,22 +27723,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M216" t="n">
         <v>3.4</v>
       </c>
       <c r="N216" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Z216" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M217" t="n">
         <v>3.4</v>
       </c>
       <c r="N217" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Z217" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28791,13 +28791,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -28830,10 +28830,10 @@
         <v>0</v>
       </c>
       <c r="Y220" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z220" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA220" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z228" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31722,22 +31722,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,16 +33345,16 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB255" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC255" t="n">
         <v>0</v>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,16 +33603,16 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA257" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB257" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,22 +34302,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,22 +34431,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35076,22 +35076,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,22 +35334,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36237,22 +36237,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z278" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36366,22 +36366,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>0</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M287" t="n">
         <v>3.4</v>
       </c>
       <c r="N287" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z287" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37563,13 +37563,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>0</v>
       </c>
       <c r="Y288" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z288" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA288" t="n">
         <v>0</v>
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37692,13 +37692,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -37731,10 +37731,10 @@
         <v>0</v>
       </c>
       <c r="Y289" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z289" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA289" t="n">
         <v>0</v>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z290" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,22 +38043,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -38182,12 +38182,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N293" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -38247,10 +38247,10 @@
         <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z293" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA293" t="n">
         <v>0</v>
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z295" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA295" t="n">
         <v>0</v>
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40143,13 +40143,13 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M308" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N308" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O308" t="n">
         <v>0</v>
@@ -40182,10 +40182,10 @@
         <v>0</v>
       </c>
       <c r="Y308" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z308" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA308" t="n">
         <v>0</v>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N309" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
@@ -40311,10 +40311,10 @@
         <v>0</v>
       </c>
       <c r="Y309" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z309" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA309" t="n">
         <v>0</v>
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41175,13 +41175,13 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
@@ -41214,10 +41214,10 @@
         <v>0</v>
       </c>
       <c r="Y316" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z316" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA316" t="n">
         <v>0</v>
@@ -41397,7 +41397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G319" t="n">

--- a/jogos_2025-09-28.xlsx
+++ b/jogos_2025-09-28.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="M65" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N65" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="M66" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,16 +8964,16 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="Z66" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M80" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>7.78</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,61 +12924,61 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="M97" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N97" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,61 +13053,61 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M119" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N119" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="M120" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N120" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="M121" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,16 +16317,16 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,16 +16446,16 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>
@@ -18306,22 +18306,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21144,22 +21144,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23079,22 +23079,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23208,22 +23208,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z177" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24063,10 +24063,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24321,10 +24321,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,22 +24756,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,22 +24885,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25788,22 +25788,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.63</v>
+        <v>4.13</v>
       </c>
       <c r="M197" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N197" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="M216" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N216" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Z216" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M217" t="n">
         <v>3.4</v>
       </c>
       <c r="N217" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Z217" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,22 +31722,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,16 +33603,16 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,22 +34431,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,16 +34635,16 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z265" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA265" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB265" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35076,22 +35076,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35334,22 +35334,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35628,13 +35628,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -35667,10 +35667,10 @@
         <v>0</v>
       </c>
       <c r="Y273" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z273" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA273" t="n">
         <v>0</v>
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35757,13 +35757,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="M274" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N274" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -35796,10 +35796,10 @@
         <v>0</v>
       </c>
       <c r="Y274" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z274" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z274" t="n">
-        <v>1.85</v>
       </c>
       <c r="AA274" t="n">
         <v>0</v>
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35886,13 +35886,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -35925,10 +35925,10 @@
         <v>0</v>
       </c>
       <c r="Y275" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z275" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA275" t="n">
         <v>0</v>
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>5</v>
+        <v>1.65</v>
       </c>
       <c r="M276" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N276" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,10 +36054,10 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z276" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA276" t="n">
         <v>0</v>
@@ -36108,22 +36108,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36237,22 +36237,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36366,22 +36366,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36624,22 +36624,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M286" t="n">
         <v>3.4</v>
       </c>
       <c r="N286" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z286" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M287" t="n">
         <v>3.4</v>
       </c>
       <c r="N287" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z287" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37692,13 +37692,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -37731,10 +37731,10 @@
         <v>0</v>
       </c>
       <c r="Y289" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z289" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA289" t="n">
         <v>0</v>
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z290" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z291" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,22 +38043,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z295" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA295" t="n">
         <v>0</v>
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -39988,12 +39988,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40143,13 +40143,13 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N308" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O308" t="n">
         <v>0</v>
@@ -40182,10 +40182,10 @@
         <v>0</v>
       </c>
       <c r="Y308" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z308" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA308" t="n">
         <v>0</v>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M309" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N309" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
@@ -40311,10 +40311,10 @@
         <v>0</v>
       </c>
       <c r="Y309" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z309" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA309" t="n">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z314" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41046,13 +41046,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -41085,10 +41085,10 @@
         <v>0</v>
       </c>
       <c r="Y315" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z315" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA315" t="n">
         <v>0</v>
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G319" t="n">

--- a/jogos_2025-09-28.xlsx
+++ b/jogos_2025-09-28.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.14</v>
+        <v>3.85</v>
       </c>
       <c r="M65" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="M68" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.85</v>
+        <v>1.28</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>5.62</v>
       </c>
       <c r="N76" t="n">
-        <v>2.55</v>
+        <v>7.78</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10776,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,49 +10989,49 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
         <v>2.35</v>
       </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z82" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="M84" t="n">
-        <v>5.62</v>
+        <v>4.4</v>
       </c>
       <c r="N84" t="n">
-        <v>7.78</v>
+        <v>5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M102" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="N102" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.75</v>
+        <v>1.39</v>
       </c>
       <c r="M120" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="N120" t="n">
-        <v>1.89</v>
+        <v>5.6</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>9.6</v>
+        <v>3.15</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,16 +16446,16 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,16 +16575,16 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,22 +21918,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,22 +22047,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="M177" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N177" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z177" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z180" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23934,10 +23934,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24063,10 +24063,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25788,22 +25788,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26340,13 +26340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z235" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31668,10 +31668,10 @@
         <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA242" t="n">
         <v>0</v>
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,22 +31851,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,22 +34431,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,16 +34635,16 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z265" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA265" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB265" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,22 +34947,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35151,16 +35151,16 @@
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA269" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB269" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC269" t="n">
         <v>0</v>
@@ -35205,22 +35205,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35886,13 +35886,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>4.8</v>
+        <v>1.65</v>
       </c>
       <c r="M275" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N275" t="n">
-        <v>1.61</v>
+        <v>5.4</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -35925,10 +35925,10 @@
         <v>0</v>
       </c>
       <c r="Y275" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Z275" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA275" t="n">
         <v>0</v>
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>1.65</v>
+        <v>4.8</v>
       </c>
       <c r="M276" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N276" t="n">
-        <v>5.4</v>
+        <v>1.61</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,10 +36054,10 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z276" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AA276" t="n">
         <v>0</v>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36237,22 +36237,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>0</v>
       </c>
       <c r="Y279" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z279" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36624,22 +36624,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37563,13 +37563,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>0</v>
       </c>
       <c r="Y288" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z288" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA288" t="n">
         <v>0</v>
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G316" t="n">
